--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_351_R36.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_351_R36.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.452</v>
+        <v>7.823</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0143</v>
+        <v>6.4861</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4377</v>
+        <v>1.3369</v>
       </c>
       <c r="G2" t="n">
         <v>5.2492</v>
@@ -610,13 +610,13 @@
         <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6374</v>
+        <v>-0.2664</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6563</v>
+        <v>-0.1845</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0189</v>
+        <v>-0.0819</v>
       </c>
       <c r="V2" t="n">
         <v>2.1444</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5169</v>
+        <v>4.5306</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6493</v>
+        <v>4.8983</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1324</v>
+        <v>-0.3676</v>
       </c>
       <c r="G3" t="n">
         <v>4.2721</v>
@@ -688,13 +688,13 @@
         <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3016</v>
+        <v>0.3154</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8338</v>
+        <v>0.0828</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4679</v>
+        <v>0.2326</v>
       </c>
       <c r="V3" t="n">
         <v>-2.1444</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. FORREST</t>
+          <t>M. NOWELL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0397</v>
+        <v>3.4869</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3492</v>
+        <v>2.7639</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3095</v>
+        <v>0.7229</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2386</v>
+        <v>2.0881</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.0768</v>
+        <v>1.3254</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3154</v>
+        <v>0.7627</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4119</v>
+        <v>3.2286</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1744</v>
+        <v>2.2519</v>
       </c>
       <c r="L4" t="n">
-        <v>2.5863</v>
+        <v>0.9768</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.1733</v>
+        <v>-1.1405</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.9024</v>
+        <v>-0.9265</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2708</v>
+        <v>-0.214</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.7834</v>
+        <v>-1.3917</v>
       </c>
       <c r="R4" t="n">
         <v>2.5515</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06900000000000001</v>
+        <v>-0.1553</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6844</v>
+        <v>-0.1452</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6155</v>
+        <v>-0.0101</v>
       </c>
       <c r="V4" t="n">
-        <v>2.9641</v>
+        <v>0.3943</v>
       </c>
       <c r="W4" t="n">
-        <v>4.0363</v>
+        <v>1.0722</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0722</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. NOWELL</t>
+          <t>T. FORREST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8567</v>
+        <v>2.7181</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3354</v>
+        <v>3.5235</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5213</v>
+        <v>-0.8054</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0881</v>
+        <v>0.2386</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3254</v>
+        <v>-2.0768</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7627</v>
+        <v>2.3154</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2286</v>
+        <v>2.4119</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2519</v>
+        <v>-0.1744</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9768</v>
+        <v>2.5863</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1405</v>
+        <v>-2.1733</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9265</v>
+        <v>-1.9024</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.214</v>
+        <v>-0.2708</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.3917</v>
+        <v>-2.7834</v>
       </c>
       <c r="R5" t="n">
         <v>2.5515</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7855</v>
+        <v>-0.2526</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5737</v>
+        <v>-0.1412</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2117</v>
+        <v>-0.1114</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3943</v>
+        <v>2.9641</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0722</v>
+        <v>4.0363</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2419</v>
+        <v>2.6459</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2062</v>
+        <v>2.4421</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0357</v>
+        <v>0.2037</v>
       </c>
       <c r="G6" t="n">
         <v>2.5142</v>
@@ -922,13 +922,13 @@
         <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5917</v>
+        <v>-0.1878</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4402</v>
+        <v>-0.2043</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1516</v>
+        <v>0.0165</v>
       </c>
       <c r="V6" t="n">
         <v>-1.0722</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7338</v>
+        <v>1.3635</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1285</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.4709</v>
       </c>
       <c r="G7" t="n">
         <v>0.0173</v>
@@ -1000,13 +1000,13 @@
         <v>2.5515</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3585</v>
+        <v>-0.0119</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2513</v>
+        <v>-0.4872</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6098</v>
+        <v>0.4753</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9615</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8181</v>
+        <v>-0.4142</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0999</v>
+        <v>0.136</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7181999999999999</v>
+        <v>-0.5502</v>
       </c>
       <c r="G8" t="n">
         <v>0.5313</v>
@@ -1078,13 +1078,13 @@
         <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5091</v>
+        <v>-0.1052</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.224</v>
+        <v>0.0119</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2851</v>
+        <v>-0.1171</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0722</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7575</v>
+        <v>-1.9188</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5198</v>
+        <v>-2.681</v>
       </c>
       <c r="F9" t="n">
         <v>0.7622</v>
@@ -1156,10 +1156,10 @@
         <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0747</v>
+        <v>-0.2359</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4955</v>
+        <v>0.3343</v>
       </c>
       <c r="U9" t="n">
         <v>-0.5702</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0382</v>
+        <v>-3.1137</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3314</v>
+        <v>-2.9029</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2933</v>
+        <v>-0.2108</v>
       </c>
       <c r="G10" t="n">
         <v>-1.0306</v>
@@ -1234,13 +1234,13 @@
         <v>3.0154</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2965</v>
+        <v>0.221</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.731</v>
+        <v>-0.3025</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0275</v>
+        <v>0.5234</v>
       </c>
       <c r="V10" t="n">
         <v>-1.6083</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5985</v>
+        <v>-4.6321</v>
       </c>
       <c r="E11" t="n">
         <v>-4.2341</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3643</v>
+        <v>-0.3979</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7847</v>
@@ -1312,13 +1312,13 @@
         <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2016</v>
+        <v>0.168</v>
       </c>
       <c r="T11" t="n">
         <v>-0.1494</v>
       </c>
       <c r="U11" t="n">
-        <v>0.351</v>
+        <v>0.3174</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.5571</v>
+        <v>-7.0443</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.7589</v>
+        <v>-7.2124</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2018</v>
+        <v>0.1682</v>
       </c>
       <c r="G12" t="n">
         <v>-3.2612</v>
@@ -1390,13 +1390,13 @@
         <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1208</v>
+        <v>0.3921</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4991</v>
+        <v>0.0474</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3782</v>
+        <v>0.3446</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.071599999999997</v>
+        <v>5.444899999999997</v>
       </c>
       <c r="E13" t="n">
-        <v>3.738799999999999</v>
+        <v>4.112099999999999</v>
       </c>
       <c r="F13" t="n">
         <v>1.3329</v>
@@ -1468,13 +1468,13 @@
         <v>19.716</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4919999999999998</v>
+        <v>-0.1185999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.5113</v>
+        <v>-1.1379</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0192</v>
+        <v>1.0191</v>
       </c>
       <c r="V13" t="n">
         <v>-1.3558</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.6837</v>
+        <v>5.9139</v>
       </c>
       <c r="E14" t="n">
-        <v>6.397</v>
+        <v>5.3354</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2867</v>
+        <v>0.5784</v>
       </c>
       <c r="G14" t="n">
         <v>2.1757</v>
@@ -1546,13 +1546,13 @@
         <v>2.7834</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3636</v>
+        <v>0.5937</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9401</v>
+        <v>-0.1215</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4235</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>2.6805</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9855</v>
+        <v>4.2544</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1357</v>
+        <v>4.0793</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1502</v>
+        <v>0.1751</v>
       </c>
       <c r="G15" t="n">
         <v>4.3603</v>
@@ -1624,13 +1624,13 @@
         <v>4.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9651</v>
+        <v>0.3038</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.411</v>
+        <v>-0.4674</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4459</v>
+        <v>0.7712</v>
       </c>
       <c r="V15" t="n">
         <v>1.214</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.823</v>
+        <v>1.9238</v>
       </c>
       <c r="E16" t="n">
         <v>3.6994</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8763</v>
+        <v>-1.7755</v>
       </c>
       <c r="G16" t="n">
         <v>1.5931</v>
@@ -1702,13 +1702,13 @@
         <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3897</v>
+        <v>0.4905</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1098</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4995</v>
+        <v>0.6002999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>0.5361</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Z. HANKINS</t>
+          <t>J. DIBARTOLOMEO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0819</v>
+        <v>1.3915</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3945</v>
+        <v>-0.7397</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4763</v>
+        <v>2.1313</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3252</v>
+        <v>-1.2465</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6231</v>
+        <v>-0.2159</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2978</v>
+        <v>-1.0305</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7327</v>
+        <v>-1.3142</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7695</v>
+        <v>0.1849</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0368</v>
+        <v>-1.4991</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4075</v>
+        <v>0.0678</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1465</v>
+        <v>-0.4008</v>
       </c>
       <c r="O17" t="n">
-        <v>0.261</v>
+        <v>0.4685</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2473</v>
+        <v>0.7824</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3383</v>
+        <v>0.4327</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.09089999999999999</v>
+        <v>0.3497</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. DIBARTOLOMEO</t>
+          <t>Z. HANKINS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6838</v>
+        <v>0.9024</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9756</v>
+        <v>-0.6304</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6595</v>
+        <v>1.5328</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2465</v>
+        <v>-0.3252</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2159</v>
+        <v>-0.6231</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0305</v>
+        <v>0.2978</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3142</v>
+        <v>-0.7327</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1849</v>
+        <v>-0.7695</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.4991</v>
+        <v>0.0368</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0678</v>
+        <v>0.4075</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4008</v>
+        <v>0.1465</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4685</v>
+        <v>0.261</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0747</v>
+        <v>0.0679</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1968</v>
+        <v>0.1024</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1221</v>
+        <v>-0.0345</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. SANTOS</t>
+          <t>J. HOARD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.034</v>
+        <v>-2.2553</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7594</v>
+        <v>-2.8466</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.7934</v>
+        <v>0.5913</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.841</v>
+        <v>-1.9429</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0155</v>
+        <v>-0.2533</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8566</v>
+        <v>-1.6895</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2083</v>
+        <v>2.3748</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5412</v>
+        <v>2.0068</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0.368</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6327</v>
+        <v>-4.3177</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-2.2601</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.107</v>
+        <v>-2.0576</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9278</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-5.7988</v>
       </c>
       <c r="R19" t="n">
-        <v>0.232</v>
+        <v>3.9432</v>
       </c>
       <c r="S19" t="n">
-        <v>1.7374</v>
+        <v>0.4709</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9856</v>
+        <v>-0.4949</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2482</v>
+        <v>0.9658</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.0026</v>
+        <v>1.0722</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8349</v>
+        <v>-2.5819</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1822</v>
+        <v>-1.8283</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6526999999999999</v>
+        <v>-0.7534999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>-3.1359</v>
@@ -2014,13 +2014,13 @@
         <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3062</v>
+        <v>0.5592</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2161</v>
+        <v>0.1377</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5223</v>
+        <v>0.4215</v>
       </c>
       <c r="V20" t="n">
         <v>-1.8608</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. HOARD</t>
+          <t>M. SANTOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8901</v>
+        <v>-3.2357</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2005</v>
+        <v>-0.6561</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3104</v>
+        <v>-2.5797</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9429</v>
+        <v>-0.841</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2533</v>
+        <v>0.0155</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6895</v>
+        <v>-0.8566</v>
       </c>
       <c r="J21" t="n">
-        <v>2.3748</v>
+        <v>-0.2083</v>
       </c>
       <c r="K21" t="n">
-        <v>2.0068</v>
+        <v>0.5412</v>
       </c>
       <c r="L21" t="n">
-        <v>0.368</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.3177</v>
+        <v>-0.6327</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.2601</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.0576</v>
+        <v>-0.107</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8556</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.7988</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>3.9432</v>
+        <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1639</v>
+        <v>0.5357</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8487</v>
+        <v>0.5702</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6849</v>
+        <v>-0.0345</v>
       </c>
       <c r="V21" t="n">
-        <v>1.0722</v>
+        <v>-2.0026</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0621</v>
+        <v>-3.4381</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2308</v>
+        <v>-2.8769</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8313</v>
+        <v>-0.5612</v>
       </c>
       <c r="G22" t="n">
         <v>-6.0383</v>
@@ -2170,13 +2170,13 @@
         <v>3.0154</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7556</v>
+        <v>-0.1316</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7741</v>
+        <v>-0.4202</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0185</v>
+        <v>0.2886</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2836</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.5083</v>
+        <v>-5.5875</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.8046</v>
+        <v>-4.3328</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7037</v>
+        <v>-1.2548</v>
       </c>
       <c r="G23" t="n">
         <v>-3.8382</v>
@@ -2248,13 +2248,13 @@
         <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.7423</v>
+        <v>-0.8215</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1202</v>
+        <v>-0.6484</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.622</v>
+        <v>-0.1731</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.0715</v>
+        <v>-2.712500000000002</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7966999999999986</v>
+        <v>-0.7966999999999995</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.2747</v>
+        <v>-1.9158</v>
       </c>
       <c r="G24" t="n">
         <v>-9.238899999999999</v>
@@ -2302,16 +2302,16 @@
         <v>9.579700000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>7.422700000000001</v>
+        <v>7.4227</v>
       </c>
       <c r="L24" t="n">
-        <v>2.156600000000001</v>
+        <v>2.1566</v>
       </c>
       <c r="M24" t="n">
         <v>-18.8184</v>
       </c>
       <c r="N24" t="n">
-        <v>-9.835699999999999</v>
+        <v>-9.835700000000001</v>
       </c>
       <c r="O24" t="n">
         <v>-8.982799999999999</v>
@@ -2326,13 +2326,13 @@
         <v>22.0355</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4920000000000002</v>
+        <v>2.851</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0191</v>
+        <v>-1.0192</v>
       </c>
       <c r="U24" t="n">
-        <v>1.5114</v>
+        <v>3.8702</v>
       </c>
       <c r="V24" t="n">
         <v>1.3558</v>
